--- a/reports/scholar_report.xlsx
+++ b/reports/scholar_report.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25 July 2026 18:25:17</t>
+          <t>26 July 2026 01:20:29</t>
         </is>
       </c>
     </row>
